--- a/daftar_sentence.xlsx
+++ b/daftar_sentence.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\vocab_streamlit\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{68F8CB8C-2A09-462C-8459-627363CD786E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBCCAD87-A1C7-4E0B-B079-CD7E4F7AAE55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{E725FEA7-0BAA-42C1-B95C-4C3BBF7F5C45}"/>
   </bookViews>
@@ -27,9 +27,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
   <si>
-    <t>Vocab</t>
-  </si>
-  <si>
     <t>Pos</t>
   </si>
   <si>
@@ -284,6 +281,9 @@
       </rPr>
       <t xml:space="preserve"> get to the airport</t>
     </r>
+  </si>
+  <si>
+    <t>Sentence</t>
   </si>
 </sst>
 </file>
@@ -687,137 +687,137 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" t="s">
         <v>4</v>
       </c>
-      <c r="C2" t="s">
-        <v>5</v>
-      </c>
       <c r="D2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" t="s">
         <v>6</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>7</v>
-      </c>
-      <c r="D3" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" t="s">
         <v>9</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>10</v>
-      </c>
-      <c r="D4" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" t="s">
         <v>12</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>13</v>
-      </c>
-      <c r="D5" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="3" t="s">
         <v>16</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" t="s">
         <v>18</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
         <v>19</v>
-      </c>
-      <c r="D7" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" t="s">
         <v>21</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>22</v>
-      </c>
-      <c r="D8" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9" t="s">
         <v>24</v>
-      </c>
-      <c r="D9" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" t="s">
         <v>27</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
         <v>28</v>
-      </c>
-      <c r="D10" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" t="s">
         <v>30</v>
       </c>
-      <c r="C11" t="s">
+      <c r="D11" t="s">
         <v>31</v>
-      </c>
-      <c r="D11" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
+        <v>33</v>
+      </c>
+      <c r="C12" t="s">
         <v>34</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
         <v>35</v>
-      </c>
-      <c r="D12" t="s">
-        <v>36</v>
       </c>
     </row>
   </sheetData>
